--- a/sheets/민요/검수/긴 아리랑 (채보3).xlsx
+++ b/sheets/민요/검수/긴 아리랑 (채보3).xlsx
@@ -409,7 +409,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -629,12 +629,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|無潢無</t>
+          <t xml:space="preserve">–|無潢無</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無潢無</t>
         </is>
       </c>
@@ -709,12 +709,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I6" s="2"/>
@@ -744,12 +744,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I7" s="2"/>
@@ -779,13 +779,13 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞南|―|㴌㳞潢</t>
+          <t xml:space="preserve">㳞南|–|㴌㳞潢</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞南
-―
+–
 㴌㳞潢</t>
         </is>
       </c>
@@ -856,13 +856,13 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|―姑</t>
+          <t xml:space="preserve">–|–姑</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―姑</t>
+          <t xml:space="preserve">–
+–姑</t>
         </is>
       </c>
       <c r="I10" s="3"/>
@@ -931,12 +931,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|無潢無</t>
+          <t xml:space="preserve">–|無潢無</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無潢無</t>
         </is>
       </c>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|無潢無</t>
+          <t xml:space="preserve">–|無潢無</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無潢無</t>
         </is>
       </c>
@@ -1269,12 +1269,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I21" s="2"/>
@@ -1304,13 +1304,13 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|―姑</t>
+          <t xml:space="preserve">–|–姑</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―姑</t>
+          <t xml:space="preserve">–
+–姑</t>
         </is>
       </c>
       <c r="I22" s="3"/>
@@ -1383,12 +1383,12 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I24" s="2"/>
@@ -1498,12 +1498,12 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I27" s="2"/>
@@ -1533,12 +1533,12 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -1648,12 +1648,12 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|潢|無南</t>
+          <t xml:space="preserve">–|潢|無南</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 潢
 無南</t>
         </is>
@@ -1725,12 +1725,12 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|潢|無南</t>
+          <t xml:space="preserve">–|潢|無南</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 潢
 無南</t>
         </is>
@@ -1877,12 +1877,12 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I37" s="2"/>
@@ -2028,12 +2028,12 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|南潢△</t>
+          <t xml:space="preserve">–|南潢△</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南潢△</t>
         </is>
       </c>
@@ -2104,14 +2104,14 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲姑|仲姑|―</t>
+          <t xml:space="preserve">仲姑|仲姑|–</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑
 仲姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I44" s="2"/>
@@ -2219,12 +2219,12 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I46" s="2"/>
@@ -2254,12 +2254,12 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|ﾉ</t>
+          <t xml:space="preserve">–|ﾉ</t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ﾉ</t>
         </is>
       </c>
@@ -2358,19 +2358,19 @@
       <c r="A4" s="0"/>
       <c r="B4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C4" s="9"/>
       <c r="D4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E4" s="9"/>
       <c r="F4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無潢無</t>
         </is>
       </c>
@@ -2399,7 +2399,7 @@
       <c r="C5" s="10"/>
       <c r="D5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -2414,7 +2414,7 @@
       <c r="G5" s="10"/>
       <c r="H5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無潢無</t>
         </is>
       </c>
@@ -2496,7 +2496,7 @@
       <c r="G7" s="9"/>
       <c r="H7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I7" s="9"/>
@@ -2505,14 +2505,14 @@
       <c r="A8" s="0"/>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南潢△</t>
         </is>
       </c>
       <c r="C8" s="10"/>
       <c r="D8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 潢
 無南</t>
         </is>
@@ -2526,7 +2526,7 @@
       <c r="G8" s="10"/>
       <c r="H8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I8" s="10"/>
@@ -2569,7 +2569,7 @@
       <c r="H9" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞南
-―
+–
 㴌㳞潢</t>
         </is>
       </c>
@@ -2581,7 +2581,7 @@
         <is>
           <t xml:space="preserve">仲姑
 仲姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="D10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 潢
 無南</t>
         </is>
@@ -2599,7 +2599,7 @@
       <c r="E10" s="9"/>
       <c r="F10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G10" s="9"/>
@@ -2615,7 +2615,7 @@
       <c r="A11" s="0"/>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C11" s="10"/>
@@ -2628,15 +2628,15 @@
       <c r="E11" s="13"/>
       <c r="F11" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―姑</t>
+          <t xml:space="preserve">–
+–姑</t>
         </is>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―姑</t>
+          <t xml:space="preserve">–
+–姑</t>
         </is>
       </c>
       <c r="I11" s="13"/>
@@ -2676,7 +2676,7 @@
       <c r="A13" s="0"/>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C13" s="9"/>
@@ -2684,13 +2684,13 @@
       <c r="E13" s="9"/>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G13" s="9"/>
       <c r="H13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無潢無</t>
         </is>
       </c>
@@ -2700,7 +2700,7 @@
       <c r="A14" s="0"/>
       <c r="B14" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ﾉ</t>
         </is>
       </c>

--- a/sheets/민요/검수/긴 아리랑 (채보3).xlsx
+++ b/sheets/민요/검수/긴 아리랑 (채보3).xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2295,60 +2336,60 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">긴 아리랑</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아라</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無
 南</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">났</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑仲
 南無南</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -2356,32 +2397,32 @@
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="C4" s="23"/>
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="E4" s="23"/>
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無潢無</t>
         </is>
       </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="G4" s="23"/>
+      <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢無
 南</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="I4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
@@ -2389,78 +2430,78 @@
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑仲
 △
 姑仲</t>
         </is>
       </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="C5" s="24"/>
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="E5" s="10"/>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="E5" s="24"/>
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑
 仲
 ·</t>
         </is>
       </c>
-      <c r="G5" s="10"/>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="G5" s="24"/>
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無潢無</t>
         </is>
       </c>
-      <c r="I5" s="10"/>
+      <c r="I5" s="24"/>
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南無南
 潢無</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無
 南無南</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
-      <c r="H6" s="18" t="inlineStr">
+      <c r="H6" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">南潢
 㴌</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr">
+      <c r="I6" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">리가</t>
         </is>
@@ -2468,260 +2509,260 @@
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G7" s="9"/>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="G7" s="23"/>
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I7" s="9"/>
+      <c r="I7" s="23"/>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 南潢△</t>
         </is>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="C8" s="24"/>
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 潢
 無南</t>
         </is>
       </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="E8" s="24"/>
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G8" s="10"/>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="G8" s="24"/>
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I8" s="10"/>
+      <c r="I8" s="24"/>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢無
 南無南</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">났</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無
 南</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="F9" s="18" t="inlineStr">
+      <c r="F9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢無
 㴌潢</t>
         </is>
       </c>
-      <c r="G9" s="11" t="inlineStr">
+      <c r="G9" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="H9" s="18" t="inlineStr">
+      <c r="H9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞南
 –
 㴌㳞潢</t>
         </is>
       </c>
-      <c r="I9" s="11"/>
+      <c r="I9" s="26"/>
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑
 仲姑
 –</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 潢
 無南</t>
         </is>
       </c>
-      <c r="E10" s="9"/>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="E10" s="23"/>
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G10" s="9"/>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="G10" s="23"/>
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞潢
 潢</t>
         </is>
       </c>
-      <c r="I10" s="9"/>
+      <c r="I10" s="23"/>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="C11" s="24"/>
+      <c r="D11" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑
 仲</t>
         </is>
       </c>
-      <c r="E11" s="13"/>
-      <c r="F11" s="18" t="inlineStr">
+      <c r="E11" s="28"/>
+      <c r="F11" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 –姑</t>
         </is>
       </c>
-      <c r="G11" s="13"/>
-      <c r="H11" s="18" t="inlineStr">
+      <c r="G11" s="28"/>
+      <c r="H11" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 –姑</t>
         </is>
       </c>
-      <c r="I11" s="13"/>
+      <c r="I11" s="28"/>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="C12" s="22"/>
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E12" s="8"/>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="E12" s="22"/>
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I12" s="8"/>
+      <c r="I12" s="22"/>
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="C13" s="23"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="G13" s="23"/>
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無潢無</t>
         </is>
       </c>
-      <c r="I13" s="9"/>
+      <c r="I13" s="23"/>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 ﾉ</t>
         </is>
       </c>
-      <c r="C14" s="13"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="18" t="inlineStr">
+      <c r="C14" s="28"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌潢
 無</t>
         </is>
       </c>
-      <c r="G14" s="13"/>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="G14" s="28"/>
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南潢
 △
 無潢無</t>
         </is>
       </c>
-      <c r="I14" s="10"/>
+      <c r="I14" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/긴 아리랑 (채보3).xlsx
+++ b/sheets/민요/검수/긴 아리랑 (채보3).xlsx
@@ -2321,20 +2321,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="82.06" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
       <c r="H2" s="20"/>
       <c r="I2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="82.06" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="82.06" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="82.06" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         <is>
           <t xml:space="preserve">仲姑
 仲
-·</t>
+–</t>
         </is>
       </c>
       <c r="G5" s="24"/>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="I5" s="24"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="82.06" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="82.06" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="F7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G7" s="23"/>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="I7" s="23"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="82.06" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
       <c r="E8" s="24"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G8" s="24"/>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="I8" s="24"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="82.06" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="I9" s="26"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="82.06" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="25" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
       </c>
       <c r="I10" s="23"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="82.06" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -2682,11 +2682,11 @@
       </c>
       <c r="I11" s="28"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="82.06" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C12" s="22"/>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="I12" s="22"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="82.06" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
       </c>
       <c r="I13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="82.06" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="25" t="inlineStr">
         <is>

--- a/sheets/민요/검수/긴 아리랑 (채보3).xlsx
+++ b/sheets/민요/검수/긴 아리랑 (채보3).xlsx
@@ -2359,7 +2359,8 @@
       </c>
       <c r="C3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">아라</t>
+          <t xml:space="preserve">아
+라</t>
         </is>
       </c>
       <c r="D3" s="21" t="inlineStr">
@@ -2503,7 +2504,8 @@
       </c>
       <c r="I6" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">리가</t>
+          <t xml:space="preserve">리
+가</t>
         </is>
       </c>
     </row>

--- a/sheets/민요/검수/긴 아리랑 (채보3).xlsx
+++ b/sheets/민요/검수/긴 아리랑 (채보3).xlsx
@@ -413,7 +413,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -423,7 +422,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -438,7 +436,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -447,17 +445,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
@@ -490,6 +488,12 @@
       <sz val="24"/>
       <name val="궁서체"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -582,7 +586,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -640,6 +644,50 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2492,272 +2540,272 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="16" width="6"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
     </row>
     <row r="3" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="19" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="7" t="s">
+      <c r="C4" s="20"/>
+      <c r="D4" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="7" t="s">
+      <c r="E4" s="20"/>
+      <c r="F4" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="7" t="s">
+      <c r="G4" s="20"/>
+      <c r="H4" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="20" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="7" t="s">
+      <c r="C5" s="21"/>
+      <c r="D5" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="E5" s="10"/>
-      <c r="F5" s="7" t="s">
+      <c r="E5" s="21"/>
+      <c r="F5" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="G5" s="10"/>
-      <c r="H5" s="7" t="s">
+      <c r="G5" s="21"/>
+      <c r="H5" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="I5" s="10"/>
+      <c r="I5" s="21"/>
     </row>
     <row r="6" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="H6" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="I6" s="12" t="s">
+      <c r="I6" s="23" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="G7" s="9"/>
-      <c r="H7" s="7" t="s">
+      <c r="G7" s="20"/>
+      <c r="H7" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="I7" s="9"/>
+      <c r="I7" s="20"/>
     </row>
     <row r="8" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="7" t="s">
+      <c r="C8" s="21"/>
+      <c r="D8" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="7" t="s">
+      <c r="E8" s="21"/>
+      <c r="F8" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="G8" s="10"/>
-      <c r="H8" s="7" t="s">
+      <c r="G8" s="21"/>
+      <c r="H8" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="I8" s="10"/>
+      <c r="I8" s="21"/>
     </row>
     <row r="9" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="G9" s="12" t="s">
+      <c r="G9" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="H9" s="11" t="s">
+      <c r="H9" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="I9" s="12"/>
+      <c r="I9" s="23"/>
     </row>
     <row r="10" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="E10" s="9"/>
-      <c r="F10" s="7" t="s">
+      <c r="E10" s="20"/>
+      <c r="F10" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="G10" s="9"/>
-      <c r="H10" s="7" t="s">
+      <c r="G10" s="20"/>
+      <c r="H10" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="I10" s="9"/>
+      <c r="I10" s="20"/>
     </row>
     <row r="11" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="11" t="s">
+      <c r="C11" s="21"/>
+      <c r="D11" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="E11" s="14"/>
-      <c r="F11" s="11" t="s">
+      <c r="E11" s="25"/>
+      <c r="F11" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="G11" s="14"/>
-      <c r="H11" s="11" t="s">
+      <c r="G11" s="25"/>
+      <c r="H11" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="I11" s="14"/>
+      <c r="I11" s="25"/>
     </row>
     <row r="12" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="7" t="s">
+      <c r="C12" s="19"/>
+      <c r="D12" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="E12" s="8"/>
-      <c r="F12" s="7" t="s">
+      <c r="E12" s="19"/>
+      <c r="F12" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="G12" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="H12" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="I12" s="8"/>
+      <c r="I12" s="19"/>
     </row>
     <row r="13" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="7" t="s">
+      <c r="C13" s="20"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="7" t="s">
+      <c r="G13" s="20"/>
+      <c r="H13" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="I13" s="9"/>
+      <c r="I13" s="20"/>
     </row>
     <row r="14" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="C14" s="14"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="11" t="s">
+      <c r="C14" s="25"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="G14" s="14"/>
-      <c r="H14" s="7" t="s">
+      <c r="G14" s="25"/>
+      <c r="H14" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="I14" s="10"/>
+      <c r="I14" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/긴 아리랑 (채보3).xlsx
+++ b/sheets/민요/검수/긴 아리랑 (채보3).xlsx
@@ -510,10 +510,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="5">

--- a/sheets/민요/검수/긴 아리랑 (채보3).xlsx
+++ b/sheets/민요/검수/긴 아리랑 (채보3).xlsx
@@ -411,22 +411,8 @@
 가</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">–
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">△</t>
-    </r>
+    <t xml:space="preserve">–
+△</t>
   </si>
 </sst>
 </file>
@@ -2531,7 +2517,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="B1:I14"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
@@ -2547,8 +2533,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="16" width="6"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="60.61" customHeight="true">
       <c r="B2" s="17" t="s">
         <v>0</v>
       </c>
@@ -2560,7 +2546,7 @@
       <c r="H2" s="17"/>
       <c r="I2" s="17"/>
     </row>
-    <row r="3" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
       <c r="B3" s="18" t="s">
         <v>97</v>
       </c>
@@ -2586,7 +2572,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
       <c r="B4" s="18" t="s">
         <v>58</v>
       </c>
@@ -2606,7 +2592,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
       <c r="B5" s="18" t="s">
         <v>100</v>
       </c>
@@ -2624,7 +2610,7 @@
       </c>
       <c r="I5" s="21"/>
     </row>
-    <row r="6" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
       <c r="B6" s="18" t="s">
         <v>102</v>
       </c>
@@ -2650,7 +2636,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
       <c r="B7" s="18" t="s">
         <v>70</v>
       </c>
@@ -2672,7 +2658,7 @@
       </c>
       <c r="I7" s="20"/>
     </row>
-    <row r="8" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
       <c r="B8" s="18" t="s">
         <v>105</v>
       </c>
@@ -2690,7 +2676,7 @@
       </c>
       <c r="I8" s="21"/>
     </row>
-    <row r="9" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
       <c r="B9" s="18" t="s">
         <v>107</v>
       </c>
@@ -2714,7 +2700,7 @@
       </c>
       <c r="I9" s="23"/>
     </row>
-    <row r="10" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
       <c r="B10" s="22" t="s">
         <v>109</v>
       </c>
@@ -2734,7 +2720,7 @@
       </c>
       <c r="I10" s="20"/>
     </row>
-    <row r="11" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
       <c r="B11" s="18" t="s">
         <v>58</v>
       </c>
@@ -2752,7 +2738,7 @@
       </c>
       <c r="I11" s="25"/>
     </row>
-    <row r="12" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
       <c r="B12" s="18" t="s">
         <v>58</v>
       </c>
@@ -2772,7 +2758,7 @@
       </c>
       <c r="I12" s="19"/>
     </row>
-    <row r="13" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
       <c r="B13" s="18" t="s">
         <v>58</v>
       </c>
@@ -2788,7 +2774,7 @@
       </c>
       <c r="I13" s="20"/>
     </row>
-    <row r="14" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
       <c r="B14" s="22" t="s">
         <v>117</v>
       </c>
@@ -2810,7 +2796,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="66"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/sheets/민요/검수/긴 아리랑 (채보3).xlsx
+++ b/sheets/민요/검수/긴 아리랑 (채보3).xlsx
@@ -2523,13 +2523,13 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="15.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="15.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="15.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="15.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="16" width="6"/>
   </cols>
   <sheetData>
